--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488298_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488298_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.8788</v>
+        <v>8.9849</v>
       </c>
       <c r="E2" t="n">
-        <v>6.486</v>
+        <v>5.5182</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3928</v>
+        <v>3.4667</v>
       </c>
       <c r="G2" t="n">
         <v>6.1996</v>
@@ -610,13 +610,13 @@
         <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3637</v>
+        <v>0.4698</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0794</v>
+        <v>0.1116</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2842</v>
+        <v>0.3581</v>
       </c>
       <c r="V2" t="n">
         <v>1.5744</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0478</v>
+        <v>4.755</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5761</v>
+        <v>3.4556</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4718</v>
+        <v>1.2994</v>
       </c>
       <c r="G3" t="n">
         <v>2.1683</v>
@@ -688,13 +688,13 @@
         <v>2.9646</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5825</v>
+        <v>0.2898</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9153</v>
+        <v>-0.2052</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6673</v>
+        <v>0.4949</v>
       </c>
       <c r="V3" t="n">
         <v>0.6294</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2773</v>
+        <v>3.3124</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0788</v>
+        <v>0.7593</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3561</v>
+        <v>2.5531</v>
       </c>
       <c r="G4" t="n">
         <v>1.7892</v>
@@ -766,13 +766,13 @@
         <v>2.9646</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.494</v>
+        <v>-0.4589</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.5867</v>
+        <v>-0.7486</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0927</v>
+        <v>0.2897</v>
       </c>
       <c r="V4" t="n">
         <v>0.3144</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7105</v>
+        <v>-0.3609</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9314</v>
+        <v>-1.7788</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2209</v>
+        <v>1.4179</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0781</v>
@@ -844,13 +844,13 @@
         <v>2.594</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9294</v>
+        <v>-0.5798</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.3982</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3785</v>
+        <v>-0.1816</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0317</v>
+        <v>-0.8298</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2521</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7796</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7909</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2407</v>
+        <v>-0.0389</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2736</v>
+        <v>-0.1209</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2991</v>
+        <v>-0.9315</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2224</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0767</v>
+        <v>-1.0029</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2601</v>
@@ -1000,13 +1000,13 @@
         <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4096</v>
+        <v>-0.042</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3283</v>
+        <v>-0.0345</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0813</v>
+        <v>-0.0075</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. FROUFE PEREZ</t>
+          <t>D. RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9846</v>
+        <v>-1.9544</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.2095</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>3.225</v>
+        <v>-1.3067</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.9649</v>
+        <v>-2.0118</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.361</v>
+        <v>-1.7462</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3961</v>
+        <v>-0.2657</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.5708</v>
+        <v>-0.547</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.7071</v>
+        <v>-0.5884</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1363</v>
+        <v>0.0415</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3941</v>
+        <v>-1.4648</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6538</v>
+        <v>-1.1577</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2597</v>
+        <v>-0.3071</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1499</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.594</v>
+        <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2774</v>
+        <v>0.0012</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0621</v>
+        <v>-0.1007</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3395</v>
+        <v>0.102</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2589</v>
+        <v>-0.3144</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>-0.3144</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GARCIA</t>
+          <t>A. FROUFE PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3762</v>
+        <v>-2.5208</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0941</v>
+        <v>-5.1548</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2821</v>
+        <v>2.6341</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0118</v>
+        <v>-3.9649</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7462</v>
+        <v>-5.361</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2657</v>
+        <v>1.3961</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.547</v>
+        <v>-3.5708</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5884</v>
+        <v>-3.7071</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0415</v>
+        <v>0.1363</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4648</v>
+        <v>-0.3941</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1577</v>
+        <v>-1.6538</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3071</v>
+        <v>1.2597</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3706</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.1499</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3706</v>
+        <v>2.594</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4206</v>
+        <v>0.7411</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5471</v>
+        <v>-0.0074</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1266</v>
+        <v>0.7486</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X9" t="n">
         <v>-0.3144</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1364</v>
+        <v>-3.0325</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7362</v>
+        <v>-1.6814</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4003</v>
+        <v>-1.351</v>
       </c>
       <c r="G10" t="n">
         <v>-3.1977</v>
@@ -1234,13 +1234,13 @@
         <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0679</v>
+        <v>0.0361</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1131</v>
+        <v>-0.0584</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0453</v>
+        <v>0.0945</v>
       </c>
       <c r="V10" t="n">
         <v>0.3144</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0473</v>
+        <v>-3.2573</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5362</v>
+        <v>-3.8939</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4888</v>
+        <v>0.6365</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7614</v>
@@ -1312,13 +1312,13 @@
         <v>1.1117</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7857</v>
+        <v>0.0044</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8207</v>
+        <v>-0.1784</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0351</v>
+        <v>0.1828</v>
       </c>
       <c r="V11" t="n">
         <v>0.3144</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.618100000000002</v>
+        <v>4.165099999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.998600000000001</v>
+        <v>-3.4516</v>
       </c>
       <c r="F12" t="n">
-        <v>7.616700000000001</v>
+        <v>7.6168</v>
       </c>
       <c r="G12" t="n">
         <v>-5.907799999999999</v>
@@ -1390,13 +1390,13 @@
         <v>16.6758</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1242999999999996</v>
+        <v>0.4228000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.2878</v>
+        <v>-1.7407</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1637</v>
+        <v>2.1636</v>
       </c>
       <c r="V12" t="n">
         <v>4.0915</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.8646</v>
+        <v>7.1282</v>
       </c>
       <c r="E13" t="n">
-        <v>6.8682</v>
+        <v>6.4765</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9964</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>8.617100000000001</v>
@@ -1468,13 +1468,13 @@
         <v>1.297</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2475</v>
+        <v>0.5111</v>
       </c>
       <c r="T13" t="n">
-        <v>0.485</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7625</v>
+        <v>0.4178</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2589</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MATA PERNIA</t>
+          <t>A. GONZALEZ PALOMO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.197</v>
+        <v>0.1052</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4431</v>
+        <v>1.6316</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2461</v>
+        <v>-1.5264</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3049</v>
+        <v>1.039</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1805</v>
+        <v>1.4845</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1244</v>
+        <v>-0.4455</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2346</v>
+        <v>2.5494</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4811</v>
+        <v>1.1595</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7157</v>
+        <v>1.3899</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0703</v>
+        <v>-1.5104</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6616</v>
+        <v>0.325</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5913</v>
+        <v>-1.8354</v>
       </c>
       <c r="P16" t="n">
+        <v>-0.7411</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.9264</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-1.1117</v>
       </c>
       <c r="R16" t="n">
         <v>0.1853</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4245</v>
+        <v>0.1219</v>
       </c>
       <c r="T16" t="n">
-        <v>0.434</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0095</v>
+        <v>0.1131</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PALOMO</t>
+          <t>M. MATA PERNIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.385</v>
+        <v>-0.0974</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2399</v>
+        <v>-0.639</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6249</v>
+        <v>0.5416</v>
       </c>
       <c r="G17" t="n">
-        <v>1.039</v>
+        <v>0.3049</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4845</v>
+        <v>0.1805</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4455</v>
+        <v>0.1244</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5494</v>
+        <v>0.2346</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1595</v>
+        <v>-0.4811</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3899</v>
+        <v>0.7157</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5104</v>
+        <v>0.0703</v>
       </c>
       <c r="N17" t="n">
-        <v>0.325</v>
+        <v>0.6616</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8354</v>
+        <v>-0.5913</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7411</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>-1.1117</v>
       </c>
       <c r="R17" t="n">
         <v>0.1853</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3683</v>
+        <v>0.5241</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.383</v>
+        <v>0.2381</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0147</v>
+        <v>0.286</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9367</v>
+        <v>-0.6664</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3573</v>
+        <v>-0.2594</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5794</v>
+        <v>-0.407</v>
       </c>
       <c r="G18" t="n">
         <v>0.4307</v>
@@ -1858,13 +1858,13 @@
         <v>0.3706</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8115</v>
+        <v>-0.5413</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4832</v>
+        <v>-0.3109</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>A. ALVAREZ RICO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9373</v>
+        <v>-1.0707</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-0.0827</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0508</v>
+        <v>-0.988</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1725</v>
+        <v>0.8723</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1665</v>
+        <v>2.2162</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.006</v>
+        <v>-1.3439</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0772</v>
+        <v>1.0917</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0772</v>
+        <v>1.5372</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.4455</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2497</v>
+        <v>-0.2194</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2437</v>
+        <v>0.679</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.006</v>
+        <v>-0.8984</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3644</v>
+        <v>-0.0721</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0373</v>
+        <v>-0.2649</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4016</v>
+        <v>0.1927</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3144</v>
+        <v>-0.9444</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3144</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ALVAREZ RICO</t>
+          <t>H. ANDRADE CORREIA E SILVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0684</v>
+        <v>-1.3404</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4744</v>
+        <v>-3.3237</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.594</v>
+        <v>1.9833</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8723</v>
+        <v>-2.0515</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2162</v>
+        <v>3.0913</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3439</v>
+        <v>-5.1428</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0917</v>
+        <v>-2.3774</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5372</v>
+        <v>2.804</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4455</v>
+        <v>-5.1814</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2194</v>
+        <v>0.3259</v>
       </c>
       <c r="N20" t="n">
-        <v>0.679</v>
+        <v>0.2873</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8984</v>
+        <v>0.0386</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9264</v>
+        <v>0.9264</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8529</v>
+        <v>-1.1117</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9264</v>
+        <v>2.0382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0699</v>
+        <v>-0.2148</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6566</v>
+        <v>-0.4635</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5867</v>
+        <v>0.2487</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9444</v>
+        <v>-0.0005</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9433</v>
+        <v>0.6289</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8877</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. ANDRADE CORREIA E SILVA</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4149</v>
+        <v>-1.3659</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2258</v>
+        <v>-3.096</v>
       </c>
       <c r="F21" t="n">
-        <v>1.811</v>
+        <v>1.7301</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0515</v>
+        <v>0.4515</v>
       </c>
       <c r="H21" t="n">
-        <v>3.0913</v>
+        <v>2.5296</v>
       </c>
       <c r="I21" t="n">
-        <v>-5.1428</v>
+        <v>-2.0781</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3774</v>
+        <v>1.1836</v>
       </c>
       <c r="K21" t="n">
-        <v>2.804</v>
+        <v>1.6184</v>
       </c>
       <c r="L21" t="n">
-        <v>-5.1814</v>
+        <v>-0.4348</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3259</v>
+        <v>-0.7321</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2873</v>
+        <v>0.9112</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0386</v>
+        <v>-1.6433</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1117</v>
+        <v>-3.891</v>
       </c>
       <c r="R21" t="n">
         <v>2.0382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2892</v>
+        <v>0.0354</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3656</v>
+        <v>-0.3886</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.424</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6603</v>
+        <v>-1.4521</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2919</v>
+        <v>-1.2783</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6316</v>
+        <v>-0.1739</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4515</v>
+        <v>-1.1725</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5296</v>
+        <v>-0.1665</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0781</v>
+        <v>-1.006</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1836</v>
+        <v>0.0772</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6184</v>
+        <v>0.0772</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4348</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7321</v>
+        <v>-1.2497</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9112</v>
+        <v>-0.2437</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6433</v>
+        <v>-1.006</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.8529</v>
+        <v>0.1853</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.891</v>
+        <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0382</v>
+        <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2589</v>
+        <v>-0.1505</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5844</v>
+        <v>-0.429</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3255</v>
+        <v>0.2785</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6977</v>
+        <v>-2.09</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3686</v>
+        <v>-2.6624</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.5725</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5038</v>
@@ -2248,13 +2248,13 @@
         <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6208</v>
+        <v>0.2285</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1269</v>
+        <v>-0.1669</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4939</v>
+        <v>0.3954</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4878</v>
+        <v>-2.3899</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1259</v>
+        <v>-2.028</v>
       </c>
       <c r="F24" t="n">
         <v>-0.3618</v>
@@ -2326,10 +2326,10 @@
         <v>0.1853</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0336</v>
+        <v>0.1315</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U24" t="n">
         <v>0.143</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9079</v>
+        <v>-2.5889</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.7614</v>
+        <v>-4.5656</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8535</v>
+        <v>1.9766</v>
       </c>
       <c r="G25" t="n">
         <v>-1.0277</v>
@@ -2404,13 +2404,13 @@
         <v>1.6676</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7685</v>
+        <v>-0.4495</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7449</v>
+        <v>-0.549</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0236</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.6181</v>
+        <v>-3.618</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.6166</v>
+        <v>-7.6167</v>
       </c>
       <c r="F26" t="n">
-        <v>3.9986</v>
+        <v>3.9987</v>
       </c>
       <c r="G26" t="n">
-        <v>5.907799999999998</v>
+        <v>5.9078</v>
       </c>
       <c r="H26" t="n">
         <v>16.0459</v>
@@ -2464,13 +2464,13 @@
         <v>-2.5745</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.428300000000001</v>
+        <v>-3.4283</v>
       </c>
       <c r="N26" t="n">
         <v>4.1352</v>
       </c>
       <c r="O26" t="n">
-        <v>-7.563499999999999</v>
+        <v>-7.5635</v>
       </c>
       <c r="P26" t="n">
         <v>-5.5585</v>
@@ -2482,13 +2482,13 @@
         <v>11.1173</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1245000000000002</v>
+        <v>0.1243000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.1636</v>
+        <v>-2.1637</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2879</v>
+        <v>2.2878</v>
       </c>
       <c r="V26" t="n">
         <v>-4.0915</v>
